--- a/erp-server/erp-server-file/src/main/resources/excel/plm/orderTracking.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/plm/orderTracking.xlsx
@@ -1,23 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{00000000-0001-0000-0000-000000000000}" mc:Ignorable="x14ac xr xr2 xr3 xr6 xr10 x15">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11208"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15800" windowWidth="28040" xWindow="4240" yWindow="640"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcMode="auto"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -25,46 +27,525 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
-  <si>
-    <t xml:space="preserve">  </t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
+  <si>
+    <t>项目编号</t>
+  </si>
+  <si>
+    <t>项目名称</t>
+  </si>
+  <si>
+    <t>模具编号</t>
+  </si>
+  <si>
+    <t>模具编号(供应商)</t>
+  </si>
+  <si>
+    <t>模具状态</t>
+  </si>
+  <si>
+    <t>模具供应商</t>
+  </si>
+  <si>
+    <t>数量(套)</t>
+  </si>
+  <si>
+    <t>含税单价(￥)</t>
+  </si>
+  <si>
+    <t>税率(%)</t>
+  </si>
+  <si>
+    <t>付款方式</t>
+  </si>
+  <si>
+    <t>付款条件</t>
+  </si>
+  <si>
+    <t>关联SKU</t>
+  </si>
+  <si>
+    <t>关联产品供应商</t>
+  </si>
+  <si>
+    <t>费用返还</t>
+  </si>
+  <si>
+    <t>返还金额(￥)</t>
+  </si>
+  <si>
+    <t>返还标准</t>
+  </si>
+  <si>
+    <t>返还单量</t>
+  </si>
+  <si>
+    <t>采购数量</t>
+  </si>
+  <si>
+    <t>已收货</t>
+  </si>
+  <si>
+    <t>已入库</t>
+  </si>
+  <si>
+    <t>状态</t>
+  </si>
+  <si>
+    <t>单量差额</t>
+  </si>
+  <si>
+    <t>更新时间</t>
+  </si>
+  <si>
+    <t>{.projectNo}</t>
+  </si>
+  <si>
+    <t>{.name}</t>
+  </si>
+  <si>
+    <t>{.mouldNo}</t>
+  </si>
+  <si>
+    <t>{.thirdMouldNo}</t>
+  </si>
+  <si>
+    <t>{.statusName}</t>
+  </si>
+  <si>
+    <t>{.supplierName}</t>
+  </si>
+  <si>
+    <t>{.qty}</t>
+  </si>
+  <si>
+    <t>{.taxPrice}</t>
+  </si>
+  <si>
+    <t>{.taxRate}</t>
+  </si>
+  <si>
+    <t>{.payMethodName}</t>
+  </si>
+  <si>
+    <t>{.paymentConditionName}</t>
+  </si>
+  <si>
+    <t>{.skuNo}</t>
+  </si>
+  <si>
+    <t>{.skuSupplierName}</t>
+  </si>
+  <si>
+    <t>{.isNeedRefundName}</t>
+  </si>
+  <si>
+    <t>{.refundAmount}</t>
+  </si>
+  <si>
+    <t>{.refundStandardName}</t>
+  </si>
+  <si>
+    <t>{.refundOrderQty}</t>
+  </si>
+  <si>
+    <t>{.purchaseQty}</t>
+  </si>
+  <si>
+    <t>{.receiveQty}</t>
+  </si>
+  <si>
+    <t>{.stockInQty}</t>
+  </si>
+  <si>
+    <t>{.refundStatusName}</t>
+  </si>
+  <si>
+    <t>{.diffQty}</t>
+  </si>
+  <si>
+    <t>{.updateTime}</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="23">
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="等线"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9.75"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
-    <fill>
-      <patternFill patternType="none">
-        <fgColor/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="gray125">
-        <fgColor/>
-        <bgColor/>
+  <fills count="33">
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -73,35 +554,317 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
-      <bottom/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0">
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle builtinId="0" name="Normal" xfId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -150,7 +913,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -183,26 +946,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -235,23 +981,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -393,104 +1122,167 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{00000000-0001-0000-0000-000000000000}" mc:Ignorable="x14ac xr xr2 xr3 xr6 xr10 x15">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
-    <outlinePr summaryBelow="false" summaryRight="false"/>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="14" defaultRowHeight="19"/>
+  <dimension ref="A1:W2"/>
+  <sheetFormatPr defaultColWidth="14" defaultRowHeight="12.75" outlineLevelRow="1"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" max="10" min="10" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" max="11" min="11" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" max="12" min="12" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" max="13" min="13" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" max="14" min="14" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" max="15" min="15" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" max="16" min="16" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" max="17" min="17" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" max="18" min="18" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" max="19" min="19" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" max="20" min="20" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" max="21" min="21" style="0" width="14"/>
+    <col min="10" max="10" width="14" customWidth="1"/>
+    <col min="11" max="11" width="18.5714285714286" customWidth="1"/>
+    <col min="12" max="23" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="str">
-        <v>项目编号</v>
-      </c>
-      <c r="B1" s="1" t="str">
-        <v>项目名称</v>
-      </c>
-      <c r="C1" s="1" t="str">
-        <v>模具编号</v>
-      </c>
-      <c r="D1" s="1" t="str">
-        <v>模具编号(供应商)</v>
-      </c>
-      <c r="E1" s="1" t="str">
-        <v>模具状态</v>
-      </c>
-      <c r="F1" s="1" t="str">
-        <v>模具供应商</v>
-      </c>
-      <c r="G1" s="1" t="str">
-        <v>数量(套)</v>
-      </c>
-      <c r="H1" s="1" t="str">
-        <v>含税单价(￥)</v>
-      </c>
-      <c r="I1" s="1" t="str">
-        <v>税率(%)</v>
-      </c>
-      <c r="J1" s="1" t="str">
-        <v>付款方式</v>
-      </c>
-      <c r="K1" s="1" t="str">
-        <v>关联SKU</v>
-      </c>
-      <c r="L1" s="1" t="str">
-        <v>关联产品供应商</v>
-      </c>
-      <c r="M1" s="1" t="str">
-        <v>费用返还</v>
-      </c>
-      <c r="N1" s="1" t="str">
-        <v>返还金额(￥)</v>
-      </c>
-      <c r="O1" s="1" t="str">
-        <v>返还标准</v>
-      </c>
-      <c r="P1" s="1" t="str">
-        <v>返还单量</v>
-      </c>
-      <c r="Q1" s="1" t="str">
-        <v>采购数量</v>
-      </c>
-      <c r="R1" s="1" t="str">
-        <v>已收货</v>
-      </c>
-      <c r="S1" s="1" t="str">
-        <v>状态</v>
-      </c>
-      <c r="T1" s="1" t="str">
-        <v>单量差额</v>
-      </c>
-      <c r="U1" s="1" t="str">
-        <v>更新时间</v>
+    <row r="1" spans="1:23">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23">
+      <c r="A2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="W2" s="2" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
   <picture r:id="rId1"/>
 </worksheet>
 </file>
--- a/erp-server/erp-server-file/src/main/resources/excel/plm/orderTracking.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/plm/orderTracking.xlsx
@@ -56,7 +56,7 @@
     <t>税率(%)</t>
   </si>
   <si>
-    <t>付款方式</t>
+    <t>结算方式</t>
   </si>
   <si>
     <t>付款条件</t>
@@ -177,7 +177,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -188,13 +188,6 @@
     <font>
       <sz val="9.75"/>
       <color rgb="FF000000"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -654,159 +647,156 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1210,73 +1200,73 @@
       </c>
     </row>
     <row r="2" spans="1:23">
-      <c r="A2" s="2" t="s">
+      <c r="A2" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" t="s">
         <v>27</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" t="s">
         <v>28</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" t="s">
         <v>29</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" t="s">
         <v>30</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" t="s">
         <v>31</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" t="s">
         <v>32</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" t="s">
         <v>33</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L2" t="s">
         <v>34</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="M2" t="s">
         <v>35</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="N2" t="s">
         <v>36</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="O2" t="s">
         <v>37</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="P2" t="s">
         <v>38</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="Q2" t="s">
         <v>39</v>
       </c>
-      <c r="R2" s="2" t="s">
+      <c r="R2" t="s">
         <v>40</v>
       </c>
-      <c r="S2" s="2" t="s">
+      <c r="S2" t="s">
         <v>41</v>
       </c>
-      <c r="T2" s="2" t="s">
+      <c r="T2" t="s">
         <v>42</v>
       </c>
-      <c r="U2" s="2" t="s">
+      <c r="U2" t="s">
         <v>43</v>
       </c>
-      <c r="V2" s="2" t="s">
+      <c r="V2" t="s">
         <v>44</v>
       </c>
-      <c r="W2" s="2" t="s">
+      <c r="W2" t="s">
         <v>45</v>
       </c>
     </row>

--- a/erp-server/erp-server-file/src/main/resources/excel/plm/orderTracking.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/plm/orderTracking.xlsx
@@ -177,33 +177,26 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
-    <font>
-      <sz val="10"/>
+  <fonts count="21">
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9.75"/>
       <color rgb="FF000000"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -211,14 +204,14 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -226,7 +219,7 @@
       <b/>
       <sz val="18"/>
       <color theme="3"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -234,7 +227,7 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -242,7 +235,7 @@
       <b/>
       <sz val="15"/>
       <color theme="3"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -250,7 +243,7 @@
       <b/>
       <sz val="13"/>
       <color theme="3"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -258,14 +251,14 @@
       <b/>
       <sz val="11"/>
       <color theme="3"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -273,7 +266,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -281,7 +274,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -289,14 +282,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -304,42 +297,42 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -646,153 +639,158 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -851,7 +849,221 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <dxfs count="17">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="double">
+          <color theme="4"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color theme="4"/>
+        </left>
+        <right style="thin">
+          <color theme="4"/>
+        </right>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+        <horizontal style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
+  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+    </tableStyle>
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+    </tableStyle>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -861,9 +1073,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="WPS">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="WPS">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -877,38 +1089,38 @@
         <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4874CB"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="EE822F"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="F2BA02"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="75BD42"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="30C0B4"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="E54C5E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0026E5"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="7E1FAD"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="WPS">
       <a:majorFont>
         <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -941,9 +1153,9 @@
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -973,66 +1185,40 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="WPS">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:lumOff val="17500"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
-              </a:schemeClr>
+              <a:schemeClr val="phClr"/>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="2700000" scaled="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:hueOff val="-2520000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
-              </a:schemeClr>
+              <a:schemeClr val="phClr"/>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="2700000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -1046,20 +1232,38 @@
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:gradFill>
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="phClr">
+                  <a:hueOff val="-4200000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="phClr"/>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="2700000" scaled="1"/>
+          </a:gradFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="101600" dist="50800" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:schemeClr val="phClr">
+                <a:alpha val="60000"/>
+              </a:schemeClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:reflection stA="50000" endA="300" endPos="40000" dist="25400" dir="5400000" sy="-100000" algn="bl" rotWithShape="0"/>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
@@ -1117,162 +1321,154 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
+  <sheetPr/>
   <dimension ref="A1:W2"/>
-  <sheetFormatPr defaultColWidth="14" defaultRowHeight="12.75" outlineLevelRow="1"/>
-  <cols>
-    <col min="10" max="10" width="14" customWidth="1"/>
-    <col min="11" max="11" width="18.5714285714286" customWidth="1"/>
-    <col min="12" max="23" width="14" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <sheetData>
-    <row r="1" spans="1:23">
-      <c r="A1" s="1" t="s">
+    <row r="1" s="1" customFormat="1" spans="1:23">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:23">
-      <c r="A2" t="s">
+    <row r="2" s="1" customFormat="1" spans="1:23">
+      <c r="A2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="M2" t="s">
+      <c r="M2" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="N2" t="s">
+      <c r="N2" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="O2" t="s">
+      <c r="O2" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="P2" t="s">
+      <c r="P2" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="Q2" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="R2" t="s">
+      <c r="R2" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="S2" t="s">
+      <c r="S2" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="T2" t="s">
+      <c r="T2" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="U2" t="s">
+      <c r="U2" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="V2" t="s">
+      <c r="V2" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="W2" t="s">
+      <c r="W2" s="1" t="s">
         <v>45</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
-  <picture r:id="rId1"/>
 </worksheet>
 </file>
--- a/erp-server/erp-server-file/src/main/resources/excel/plm/orderTracking.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/plm/orderTracking.xlsx
@@ -77,7 +77,7 @@
     <t>返还标准</t>
   </si>
   <si>
-    <t>返还单量</t>
+    <t>返还数量</t>
   </si>
   <si>
     <t>采购数量</t>

--- a/erp-server/erp-server-file/src/main/resources/excel/plm/orderTracking.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/plm/orderTracking.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
   <si>
     <t>项目编号</t>
   </si>
@@ -95,6 +95,9 @@
     <t>单量差额</t>
   </si>
   <si>
+    <t>实际返还金额(￥)</t>
+  </si>
+  <si>
     <t>更新时间</t>
   </si>
   <si>
@@ -162,6 +165,9 @@
   </si>
   <si>
     <t>{.diffQty}</t>
+  </si>
+  <si>
+    <t>{.realRefundAmount}</t>
   </si>
   <si>
     <t>{.updateTime}</t>
@@ -177,7 +183,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -191,6 +197,12 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9.8"/>
+      <color rgb="FFC77DBB"/>
+      <name val="Courier New"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -657,137 +669,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -795,6 +807,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1322,10 +1337,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
+  <dimension ref="A1:X10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <cols>
+    <col min="23" max="23" width="14.75" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:23">
+    <row r="1" s="1" customFormat="1" spans="1:24">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1395,77 +1413,86 @@
       <c r="W1" s="2" t="s">
         <v>22</v>
       </c>
+      <c r="X1" s="2" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:23">
+    <row r="2" s="1" customFormat="1" spans="1:24">
       <c r="A2" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="W2" s="1" t="s">
-        <v>45</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="X2" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" spans="22:22">
+      <c r="V10" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/erp-server/erp-server-file/src/main/resources/excel/plm/orderTracking.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/plm/orderTracking.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1340,7 +1340,7 @@
   <dimension ref="A1:X10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="23" max="23" width="14.75" customWidth="1"/>
+    <col min="23" max="23" width="27.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:24">
